--- a/tools/apple_check/serials.xlsx
+++ b/tools/apple_check/serials.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Serials" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,18 +413,4019 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Serial (dien tu o A2 xuong)</t>
+          <t>Serial</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SK17Y930LW9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SGX6Q0RWDCJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SD7MP4NMJYM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SMXYGNVTF2X</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL6YFD679GY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SMWX9PJWL9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SF2959N3QDW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SLD6G2LYK27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SF7FDJ67XF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SM3WLGF7R6R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SH1GJ3JQWV4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SDXHGQHKQDV</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SHX17CWTC2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SDQ46WQ70F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SHNX0N393C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SJ5HHHXYQ6N</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SDKJ3WPFLF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SDWJPMKM4GX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SGYVQ4G452N</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SF9K207RTF3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SJ30007P7CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SGJWLNYJ031</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SGV4QCV22ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SH5YVWX6JNV</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SD2X6QM4WH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SJCGWQLWXDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SGYJTH2WN9L</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SFH6CQ2V4JQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SGLQ37TQ6MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SJJGF403J0W</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SF99HDF65W2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SJGVWTXQ9W0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SHVVL9HDJ6W</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SCY0XRP24K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SHQY4VJTGCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SGQXRY2YWCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SHGPYFN0J9Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SFHVVTK0D35</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SCFK029YRRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SG416H9G7TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SDMY7G907LG</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SF49XKXDYD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SL4MWG3P9YK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SGCF39WWP65</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SFQL4XML9CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SCYT4VNNXMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SHYJC73MPN6</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SDY3JVQ396H</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SKX1LPMQ7NH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SKW07LJQ6T0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SCDXVG7JQ4N</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SLK4Y6V3VDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SJW6TJ247LY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SL6R3KHVV00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SH7WNTQ74J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SLCNX96WNLQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SG4TY41Q7RT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SK7VQ0X02QK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sly4hg9g34t</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SH9J26N49YN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SG7X0XY06CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SCQNKX965NR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SCXGQK2YGJD</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SJ4VHWYVV3W</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SM1796MLWQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SLM745R93Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SJKN49H9YG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SL64RK6TW9N</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SH99RDFW00F</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SC221WFJ03P</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SKJV6MX00XG</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SGTXNCDGJ4Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SJC6XHV2L4Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SHP2VCMYXP6</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SJF97PR6XG2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SFCY6XHMWYF</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SHL7C2T5QG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SF4MHQGGJ2J</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SGY4YC561YJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SF3HRPQ35N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SJLQ7MNW6PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SLNX4CH091Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SMWHX7YP9W1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SCTXGH3HJCG</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SK9M6V62CYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SK5436M9DX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SL1QXPJ49PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SFGV943VM9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SG541WPVDH7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SG3206Q16KX</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SF2R2C442XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SHP74L5005F</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SJYYV6M09JL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SDR7HYF45W7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SMY2F267P7T</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SLMW6RWM7CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SLTXR4C954K</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SD72W2W04HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SG12M4DQCVV</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SJ76X5QP6PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SFHNWTNJHC7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SHXM9WR7MG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SCM4Q29QH75</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SFQGGYL92YX</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SDJ9KXNL4G6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SJ6GDW2415Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SKFX2346W4L</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SG7NG36GCFJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SM7KQTWHJHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>sm0wqv49l29</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SJT4LQC5GQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SM46VD2D691</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SD66V5T9V94</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SJX332RQYY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SHQ34R4L34J</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SH52VXR12CK</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SH6DCGXRYYG</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SMYCPH4FW3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SGK9FPYXV4N</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SM4WW90736Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SGW9VKFJ2R0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SG564L4D7MH</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SJWP6J7K03F</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SC9V19QY41C</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SL1C2V6C0F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SF4NPR7TDF9</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SGF6L1296YT</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SGQRL4MHQQJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SFY766CFXPK</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SGPYWGK7KW9</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SFVHL73CXL9</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SF3CXT7F743</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SJ7DD4RKJYF</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SD4R20745JW</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SK9YXDKXC9K</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SHC9RPHF9F6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SJHLXYW6QY5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SJ04Y0Q7325</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SC6PP2GRJXN</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SDTQGW9X74Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SFRQ09JJFYJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SDD71MJ2GMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SL7YP4DR6WC</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SKVCVHWGP9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SMVWCXXW19Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SGHX2MQ92H9</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SGVHW7ML9TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SH951WMWPVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SD4NM09N72C</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>SGWJ4TC47YP</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SLH6PYWVXGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SDR6C4NW702</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SCDCWNQMYFX</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>SKJ4363X4MN</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SC2L4C2567D</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SCMVPHFCYRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SLK3Y3X6PK2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SHHKN6M62FH</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SFHL2LQ374W</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SC76P29002M</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SH7MD9CVP43</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SFQ9Y9FF76Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SH63LVT9W21</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SGXFMVX4K32</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SKDPG4RH29R</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SMWQH199LQF</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SDM45QX6TL6</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SF076QDG9FC</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SGHF4TMH993</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SCYD9KJ7X9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SFHHX7M7CHY</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SCVXRK45D4F</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SGWC90M79NR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SFGJY1FHY4G</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SJ6P7N7H92M</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SJ5RQ4NN44H</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SCFLQ7Y7Q57</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SDFH7GMXQLJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SGGX2RTXT2F</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SC9NF04DGT4</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SDF9K27MVNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SG2YGQ29XTP</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SCKVCFK6LJY</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SH2QDHK4HPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SCR6Q30109H</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SF7K62J71JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SFT4FV3NHQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SCG9PY7TWG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SGKG2CTXJ44</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SJKJGPPVFKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SF2ML9LR407</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SLQY97C6431</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SF794YX26GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SFD9FN0WGWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SGYJ7WK6PYF</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SCF1691KX0Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SG9L271MXY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SGXPFDVHQ95</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SFM92HGX5WN</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SD2LYFN4H5P</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SDH96NYJWHG</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SD1243GP341</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SJRVQGW9Y6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SJL24HC7R4P</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SL9G2T040G9</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SFXP4P0XPPW</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SJH2142L76H</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SFQ55CXKL4N</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SG9M39CM6HL</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SCT6H9W091V</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SJHKXKXKGXW</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>SKQHXF4CT4L</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>SD5WPNXW0FJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>SL3XX40J7P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>sm9y3lyjfqw</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>SH0QRVVMY5Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>SGJ4R9JJG9M</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>SJ43QM37DY5</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>SM3K9WV6GYJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>SDVPD6DWCJY</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>SD16R5QQ4XY</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>SHWVLWRDFWW</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>SDH96JCDQJ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SHXLHQ7405W</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>SKP7WGWQJC0</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>SM12232DH56</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>SH3YYKG34X6</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>SCVWW25R461</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>SK4D6RF7X32</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>SHWGXKL7Y7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>SCT9TFYJKY9</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>SG2TNH94N2F</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SL1PKQFW4Y5</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SM43J0QK2QF</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SG36Q9JD66Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>SF6D2W7HKF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>SFNKP24HT96</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>SGW4VF9475P</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SD4914T25M7</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SL6P29J67H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SDGDCWJV74K</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SMYGY7H5XQW</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SK4FXQ6W6FH</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>SLQ6CD64RQP</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>SM23J0VM040</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>SJ0FCFQ446N</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>SCV6RHX7K4K</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>SG9TT9KL646</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>SHFGPY66RPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>SK2FNMG7J9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SJHL4CX6JFP</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SHKGH7WM45X</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SDT2XTQ466F</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SFX7WPJWLYF</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SF66W2D009J</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SJC759Y6Q0W</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SJ9GV634KP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SJ34907C42Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SKDXK2WWC35</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SJ3VNNX62F6</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SD3YJHG6Q4M</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SHQ5VF7L02X</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SL754Y29YG3</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SCHX0N79C9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SF026V4X4W1</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SMQ9TNWNQ2T</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SHM3X14FYGW</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SMJ63H45FVP</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>sd2qw07ncy6</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>SKPQRWK6QHK</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SKH2JN74QPK</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SM2TP79P29Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>SDQNY6MTYF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>SC62TGDQ7LR</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SJ63975D2CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SHQXW3GPGW4</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SFCQ4L3DYLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SMF34H4F7D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SHV9399MXQH</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SC435V9F9RM</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SJN4X3LKGYH</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SKMX4XMJ9VY</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>SM61HWR2QY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>SDHX2X2XV3Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>SL0WVV9PJLG</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SK6D367M9RG</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SMP4R5J42LT</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SHRW21WFFP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SKVXP6NYKLG</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SLQWG4H1702</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SG3P6H60Q57</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SFK7TX447N0</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SDF6V66L7TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SHPFWR62PGX</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SJYQ2969LWX</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SKKPX2W6N09</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SLDHV4GPWRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SHRVM9L9VHX</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SF9G7X7377H</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SHHJ77XX4XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SMQ4Q9T7CD7</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SCN692Y7216</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SKWK3D4LYFG</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SCNVQK30NYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SJXW33307C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SFKW4V091FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SK9JHC37NH0</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>SL42HW3QMH9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>SC9VPQ6XPH2</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>SLQVYC43T7W</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SLP725549D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SGHYFR4W9KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SLV143WQTFM</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SH6QCF6HG6R</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SJ3F7DWJP2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SJ1XXVKT2JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>SKQ7GPH09F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SM23H25763H</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>SMXT2YRW52X</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>SJJN59FYF7D</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>SDD9R3Y4DQJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>SD66TDX29NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>SFD7G4211Q9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>SDF9XQXVT2X</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>SFFKW0XMNVR</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>SD3CHQQ9H0Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>SLY7KF2CX7X</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>SC32WTQKX00</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>SKP3JWQCP9R</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>SGQ3JH25HLQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SDJQC9L9XKV</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SJX2VNW2FJD</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SGH2GDXD4VN</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>SGP9J0LK6M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>SMGX6FV56FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>SF93QT216YN</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>SHVJPJ20935</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>SHJ0JQL02V2</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>SM2QN099XGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>SKXX67XF6N7</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>SLN2MVXVXPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>SKN3XY0C9Q0</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SHJKQ9RJXDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>SM2WVGVPMFD</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>SKN3HP2FNX0</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>F9K207RTF3</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>J30007P7CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>GJWLNYJ031</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>GV4QCV22ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>H5YVWX6JNV</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>D2X6QM4WH5</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>JCGWQLWXDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>GYJTH2WN9L</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>FH6CQ2V4JQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>JJGF403J0W</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>F99HDF65W2</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>JGVWTXQ9W0</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>HVVL9HDJ6W</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>CY0XRP24K1</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>HGPYFN0J9Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>CFK029YRRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>G416H9G7TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>DMY7G907LG</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>F49XKXDYD1</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>L4MWG3P9YK</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>GCF39WWP65</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>HYJC73MPN6</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>DY3JVQ396H</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>KW07LJQ6T0</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>LK4Y6V3VDG</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>JW6TJ247LY</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>L6R3KHVV00</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>G4TY41Q7RT</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>K7VQ0X02QK</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>LY4HG9G34T</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>H9J26N49YN</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>G7X0XY06CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>M1796MLWQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>JKN49H9YG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>L64RK6TW9N</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>C221WFJ03P</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>GTXNCDGJ4Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>JF97PR6XG2</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>HL7C2T5QG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>F4MHQGGJ2J</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>LNX4CH091Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>K9M6V62CYP</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>K5436M9DX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>L1QXPJ49PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>FGV943VM9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>G541WPVDH7</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>G3206Q16KX</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>F2R2C442XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>HP74L5005F</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>JYYV6M09JL</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>DR7HYF45W7</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>MY2F267P7T</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>LMW6RWM7CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>LTXR4C954K</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>D72W2W04HT</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>G12M4DQCVV</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>J76X5QP6PV</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>FHNWTNJHC7</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>CM4Q29QH75</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>FQGGYL92YX</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>DJ9KXNL4G6</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>J6GDW2415Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>M7KQTWHJHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>M0WQV49L29</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>JT4LQC5GQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>M46VD2D691</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>D66V5T9V94</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>HQ34R4L34J</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>MYCPH4FW3F</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>GK9FPYXV4N</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>M4WW90736Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>GW9VKFJ2R0</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>G564L4D7MH</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>JWP6J7K03F</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>C9V19QY41C</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>F4NPR7TDF9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>GF6L1296YT</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>GPYWGK7KW9</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>FVHL73CXL9</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>D4R20745JW</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>HC9RPHF9F6</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>JHLXYW6QY5</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>DTQGW9X74Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>FRQ09JJFYJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>DD71MJ2GMQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>L7YP4DR6WC</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>KVCVHWGP9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>GHX2MQ92H9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>GVHW7ML9TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>H951WMWPVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>D4NM09N72C</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>GWJ4TC47YP</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>LH6PYWVXGR</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>DR6C4NW702</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>CDCWNQMYFX</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>KJ4363X4MN</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>CMVPHFCYRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>LK3Y3X6PK2</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>HHKN6M62FH</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>FHL2LQ374W</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>C76P29002M</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>FQ9Y9FF76Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>H63LVT9W21</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>GXFMVX4K32</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>MWQH199LQF</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>DM45QX6TL6</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>GHF4TMH993</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>FHHX7M7CHY</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>GWC90M79NR</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>FGJY1FHY4G</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>J6P7N7H92M</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>J5RQ4NN44H</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>CFLQ7Y7Q57</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>DFH7GMXQLJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>GGX2RTXT2F</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>C9NF04DGT4</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>DF9K27MVNT</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>G2YGQ29XTP</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>CKVCFK6LJY</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>H2QDHK4HPV</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>CR6Q30109H</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>F7K62J71JJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>FT4FV3NHQQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>CG9PY7TWG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>GKG2CTXJ44</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>JKJGPPVFKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>LQY97C6431</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>F794YX26GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>FD9FN0WGWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>GYJ7WK6PYF</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>CF1691KX0Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>G9L271MXY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>FM92HGX5WN</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>D1243GP341</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>JRVQGW9Y6M</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>JH2142L76H</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>FQ55CXKL4N</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>G9M39CM6HL</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>CT6H9W091V</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>JHKXKXKGXW</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>KQHXF4CT4L</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>D5WPNXW0FJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>M9Y3LYJFQW</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>H0QRVVMY5Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>GJ4R9JJG9M</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>J43QM37DY5</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>M3K9WV6GYJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>D16R5QQ4XY</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>KP7WGWQJC0</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>H3YYKG34X6</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>K4D6RF7X32</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>HWGXKL7Y7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>CT9TFYJKY9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>G2TNH94N2F</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>M43J0QK2QF</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>F6D2W7HKF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>FNKP24HT96</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>GW4VF9475P</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>L6P29J67H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>MYGY7H5XQW</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>K4FXQ6W6FH</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>M23J0VM040</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>CV6RHX7K4K</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>G9TT9KL646</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>HFGPY66RPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>HKGH7WM45X</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>DT2XTQ466F</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>J9GV634KP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>J3VNNX62F6</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>D3YJHG6Q4M</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>HQ5VF7L02X</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>L754Y29YG3</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>CHX0N79C9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>F026V4X4W1</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>HM3X14FYGW</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>MJ63H45FVP</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>D2QW07NCY6</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>KPQRWK6QHK</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>KH2JN74QPK</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>DQNY6MTYF7</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>J63975D2CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>FCQ4L3DYLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>JN4X3LKGYH</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>M61HWR2QY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>DHX2X2XV3Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>K6D367M9RG</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>MP4R5J42LT</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>HRW21WFFP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>KVXP6NYKLG</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>LQWG4H1702</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>DF6V66L7TL</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>HPFWR62PGX</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>JYQ2969LWX</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>KKPX2W6N09</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>LDHV4GPWRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>HRVM9L9VHX</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>F9G7X7377H</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>HHJ77XX4XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>MQ4Q9T7CD7</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>CN692Y7216</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>KWK3D4LYFG</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>FKW4V091FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>L42HW3QMH9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>C9VPQ6XPH2</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>GHYFR4W9KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>LV143WQTFM</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>H6QCF6HG6R</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>J3F7DWJP2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>KQ7GPH09F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>M23H25763H</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>DD9R3Y4DQJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>D66TDX29NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>DF9XQXVT2X</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>FFKW0XMNVR</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>LY7KF2CX7X</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>C32WTQKX00</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>KP3JWQCP9R</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>GQ3JH25HLQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>GH2GDXD4VN</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>GP9J0LK6M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>F93QT216YN</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>HVJPJ20935</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>LN2MVXVXPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>KN3XY0C9Q0</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>HJKQ9RJXDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>M2WVGVPMFD</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>KN3HP2FNX0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
